--- a/backend/test_attendance.xlsx
+++ b/backend/test_attendance.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web dev\activity\se-lab-project-activity-points\backend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keert\Downloads\chriss\se-lab-project-activity-points\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE6D4C11-7B86-4753-8E7D-A77D49C20F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E100D4-3F95-4E5C-B1B2-C104F5BD2537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{81169CF8-658C-4641-BF0D-29139460DD1D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{81169CF8-658C-4641-BF0D-29139460DD1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,12 +42,6 @@
     <t>NAME</t>
   </si>
   <si>
-    <t>B220842CS</t>
-  </si>
-  <si>
-    <t>PRANEETH</t>
-  </si>
-  <si>
     <t>B221312EE</t>
   </si>
   <si>
@@ -58,6 +52,12 @@
   </si>
   <si>
     <t>KARTHIK</t>
+  </si>
+  <si>
+    <t>B220038CS</t>
+  </si>
+  <si>
+    <t>Keerthana</t>
   </si>
 </sst>
 </file>
@@ -411,6 +411,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC36EFF-199E-41BB-9788-322BFEA493AB}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.21875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -422,26 +425,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
